--- a/artfynd/A 29434-2023 artfynd.xlsx
+++ b/artfynd/A 29434-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29434-2023 artfynd.xlsx
+++ b/artfynd/A 29434-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111438457</v>
+        <v>111438446</v>
       </c>
       <c r="B2" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468747.5763832342</v>
+        <v>468853</v>
       </c>
       <c r="R2" t="n">
-        <v>6882880.250689426</v>
+        <v>6882801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>silverved tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,22 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111438430</v>
+        <v>111438440</v>
       </c>
       <c r="B3" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468756.5460031229</v>
+        <v>468800</v>
       </c>
       <c r="R3" t="n">
-        <v>6882784.091042386</v>
+        <v>6882795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +850,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>högstubbe björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,22 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111438446</v>
+        <v>111438428</v>
       </c>
       <c r="B4" t="n">
-        <v>77550</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468853.3954624244</v>
+        <v>468741</v>
       </c>
       <c r="R4" t="n">
-        <v>6882801.477506777</v>
+        <v>6882781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +957,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björk</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1044,16 +999,11 @@
         <v>111438444</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468841.2361184616</v>
+        <v>468841</v>
       </c>
       <c r="R5" t="n">
-        <v>6882806.276033297</v>
+        <v>6882806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,44 +1096,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111438428</v>
+        <v>111438455</v>
       </c>
       <c r="B6" t="n">
-        <v>77597</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468740.5586073888</v>
+        <v>468784</v>
       </c>
       <c r="R6" t="n">
-        <v>6882780.957796668</v>
+        <v>6882885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,21 +1171,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1192,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>björk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1278,22 +1203,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111438442</v>
+        <v>111438426</v>
       </c>
       <c r="B7" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468800.3617588138</v>
+        <v>468629</v>
       </c>
       <c r="R7" t="n">
-        <v>6882801.965499061</v>
+        <v>6882722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,21 +1278,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1299,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>silverved tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,22 +1310,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111438433</v>
+        <v>111438442</v>
       </c>
       <c r="B8" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468756.5460031229</v>
+        <v>468800</v>
       </c>
       <c r="R8" t="n">
-        <v>6882784.091042386</v>
+        <v>6882802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,21 +1385,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1406,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>silverved tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1522,22 +1417,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111438439</v>
+        <v>111438432</v>
       </c>
       <c r="B9" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468788.4775288465</v>
+        <v>468757</v>
       </c>
       <c r="R9" t="n">
-        <v>6882785.67140964</v>
+        <v>6882784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,21 +1492,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1513,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>silverved tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1644,22 +1524,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111438447</v>
+        <v>111438439</v>
       </c>
       <c r="B10" t="n">
-        <v>76495</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468866.1318338988</v>
+        <v>468788</v>
       </c>
       <c r="R10" t="n">
-        <v>6882808.390505624</v>
+        <v>6882786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,19 +1599,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,22 +1631,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111438440</v>
+        <v>111438453</v>
       </c>
       <c r="B11" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468800.2970216064</v>
+        <v>468789</v>
       </c>
       <c r="R11" t="n">
-        <v>6882794.936009536</v>
+        <v>6882885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,21 +1706,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1877,7 +1727,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>högstubbe björk</t>
+          <t>silverved tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1888,22 +1738,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111438425</v>
+        <v>111438457</v>
       </c>
       <c r="B12" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,42 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundslätt, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468571.5178632676</v>
+        <v>468748</v>
       </c>
       <c r="R12" t="n">
-        <v>6882722.999468728</v>
+        <v>6882880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,26 +1813,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2012,7 +1834,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>silverved tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2023,22 +1845,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111438453</v>
+        <v>111438435</v>
       </c>
       <c r="B13" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2070,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468789.3971357156</v>
+        <v>468755</v>
       </c>
       <c r="R13" t="n">
-        <v>6882885.489071017</v>
+        <v>6882784</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2103,19 +1920,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2145,22 +1952,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111438432</v>
+        <v>111438447</v>
       </c>
       <c r="B14" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2192,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468756.5460031229</v>
+        <v>468866</v>
       </c>
       <c r="R14" t="n">
-        <v>6882784.091042386</v>
+        <v>6882808</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,21 +2027,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2256,7 +2048,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,22 +2059,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111438455</v>
+        <v>111438425</v>
       </c>
       <c r="B15" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,34 +2077,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sundslätt, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468784.2260541836</v>
+        <v>468572</v>
       </c>
       <c r="R15" t="n">
-        <v>6882884.599394682</v>
+        <v>6882723</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,19 +2142,14 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,15 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111438426</v>
+        <v>111438430</v>
       </c>
       <c r="B16" t="n">
-        <v>76918</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,21 +2197,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2436,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468629.2461709682</v>
+        <v>468757</v>
       </c>
       <c r="R16" t="n">
-        <v>6882722.464435354</v>
+        <v>6882784</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,21 +2254,11 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2500,7 +2275,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>silverved tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2511,22 +2286,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111438435</v>
+        <v>111438433</v>
       </c>
       <c r="B17" t="n">
-        <v>76495</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2558,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468754.6686940129</v>
+        <v>468757</v>
       </c>
       <c r="R17" t="n">
-        <v>6882784.108355919</v>
+        <v>6882784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2591,19 +2361,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2633,10 +2393,224 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Karolin Hård, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111438437</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundslätt, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>468768</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6882791</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111438449</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundslätt, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468847</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6882852</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29434-2023 artfynd.xlsx
+++ b/artfynd/A 29434-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438440</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438442</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438432</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438439</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438453</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438457</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438435</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438447</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438425</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438430</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2397,6 +2477,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438433</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438437</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,8 +2701,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111438449</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>